--- a/public/human-resources-dashboard/personnel-management/FT-RH-27.xlsx
+++ b/public/human-resources-dashboard/personnel-management/FT-RH-27.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B93A576-00D2-47FD-9DD6-F6E5C5493C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C7FB0F-CBEF-4F3F-A78C-C1908E001616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,7 +91,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,6 +119,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -134,7 +140,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -166,11 +172,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -185,28 +228,46 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -223,6 +284,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -653,30 +723,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14"/>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="15" t="s">
+      <c r="A1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="16" t="s">
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
     </row>
     <row r="2" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="18" t="s">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="18"/>
+      <c r="E2" s="24"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -686,170 +756,170 @@
       <c r="H2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
     </row>
     <row r="3" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="18" t="s">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="17" t="s">
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
     </row>
     <row r="4" spans="1:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12" t="s">
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
     </row>
     <row r="7" spans="1:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12" t="s">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12" t="s">
+      <c r="H8" s="14"/>
+      <c r="I8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
     </row>
     <row r="9" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
     </row>
     <row r="10" spans="1:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11" t="s">
+      <c r="C11" s="16"/>
+      <c r="D11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11" t="s">
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="19"/>
     </row>
     <row r="12" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="27"/>
     </row>
     <row r="13" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="27"/>
     </row>
     <row r="14" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="27"/>
     </row>
     <row r="15" spans="1:11" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="27"/>
     </row>
     <row r="16" spans="1:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -858,34 +928,35 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:K11"/>
     <mergeCell ref="A1:C3"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="I1:K1"/>
@@ -899,9 +970,6 @@
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="H12:K12"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="G8:H8"/>
@@ -910,20 +978,22 @@
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="I9:K9"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:G11"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:G13"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D12:G12"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="E21:G21"/>
     <mergeCell ref="A22:D22"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:K15"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.11811023622047245" bottom="0.11811023622047245" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
